--- a/data/cammy/inputs/cammy_oki_HSA_plus11.xlsx
+++ b/data/cammy/inputs/cammy_oki_HSA_plus11.xlsx
@@ -5,16 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dfa238\pyproj\gambit_tekken8\data\eddy\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dfa238\pyproj\gambit_tekken8\data\cammy\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27B904E7-CBDB-428A-9343-6FC8592953EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D821D57-708B-450C-A8A9-902A95206E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1380" windowWidth="28815" windowHeight="14355" activeTab="1" xr2:uid="{3646A7B2-A3A2-437C-B2D0-C976E94CCFF6}"/>
+    <workbookView xWindow="735" yWindow="1845" windowWidth="28065" windowHeight="14355" activeTab="1" xr2:uid="{3646A7B2-A3A2-437C-B2D0-C976E94CCFF6}"/>
   </bookViews>
   <sheets>
     <sheet name="metadata" sheetId="2" r:id="rId1"/>
-    <sheet name="eddy_rlx1" sheetId="1" r:id="rId2"/>
+    <sheet name="cammy_oki_HSA_plus11" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,10 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="13">
-  <si>
-    <t>B</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="27">
   <si>
     <t>title</t>
   </si>
@@ -51,9 +48,6 @@
     <t>P2</t>
   </si>
   <si>
-    <t>Reina</t>
-  </si>
-  <si>
     <t>comment</t>
   </si>
   <si>
@@ -66,23 +60,71 @@
     <t>key</t>
   </si>
   <si>
-    <t>Eddy</t>
-  </si>
-  <si>
-    <t>Eddy RLX 1 on block</t>
-  </si>
-  <si>
-    <t>Eddy after RLX 1 on block (-11)</t>
-  </si>
-  <si>
-    <t>ws44</t>
+    <t>cr.HP</t>
+  </si>
+  <si>
+    <t>shimmy</t>
+  </si>
+  <si>
+    <t>throw</t>
+  </si>
+  <si>
+    <t>f.j</t>
+  </si>
+  <si>
+    <t>n.j</t>
+  </si>
+  <si>
+    <t>db</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>b.j</t>
+  </si>
+  <si>
+    <t>Cammy OKI HSA FD MS (+11)</t>
+  </si>
+  <si>
+    <t>jab</t>
+  </si>
+  <si>
+    <t>throw tech</t>
+  </si>
+  <si>
+    <t>delayed tech</t>
+  </si>
+  <si>
+    <t>reversal DP</t>
+  </si>
+  <si>
+    <t>cr.LK</t>
+  </si>
+  <si>
+    <t>Cammy OKI Heavy Spiral Arrow Forward Dash Mid Screen (+11) (yellow = scramble)</t>
+  </si>
+  <si>
+    <t>parry</t>
+  </si>
+  <si>
+    <t>delayed cr.HP</t>
+  </si>
+  <si>
+    <t>Cammy1</t>
+  </si>
+  <si>
+    <t>Cammy2</t>
+  </si>
+  <si>
+    <t>cr.MK</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -90,13 +132,37 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -108,10 +174,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -119,8 +187,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="3">
+    <cellStyle name="Bad" xfId="1" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="2" builtinId="28"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -457,47 +529,47 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.28515625" customWidth="1"/>
-    <col min="2" max="2" width="31" customWidth="1"/>
+    <col min="2" max="2" width="32.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>5</v>
-      </c>
       <c r="B5" s="1" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -507,57 +579,367 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3B9BB04-D3D2-4E07-A007-5B16E4AB0AD8}">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="3" width="9.140625" customWidth="1"/>
-    <col min="4" max="4" width="15.140625" customWidth="1"/>
-    <col min="5" max="5" width="11.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.5703125" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" customWidth="1"/>
-    <col min="10" max="11" width="22.5703125" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
+    <col min="3" max="3" width="6.28515625" customWidth="1"/>
+    <col min="4" max="4" width="7.42578125" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" customWidth="1"/>
+    <col min="6" max="6" width="8.85546875" customWidth="1"/>
+    <col min="7" max="7" width="6.5703125" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" customWidth="1"/>
+    <col min="9" max="9" width="12.28515625" customWidth="1"/>
+    <col min="10" max="10" width="11.28515625" customWidth="1"/>
+    <col min="11" max="11" width="10.85546875" customWidth="1"/>
     <col min="12" max="12" width="14" customWidth="1"/>
     <col min="13" max="13" width="12.85546875" customWidth="1"/>
     <col min="14" max="14" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" t="s">
+        <v>18</v>
+      </c>
+      <c r="J1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="3">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>2300</v>
+      </c>
+      <c r="E2">
+        <v>2300</v>
+      </c>
+      <c r="F2">
+        <v>2300</v>
+      </c>
+      <c r="G2">
+        <v>2440</v>
+      </c>
+      <c r="H2">
+        <v>2440</v>
+      </c>
+      <c r="I2" s="3">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>-2100</v>
+      </c>
+      <c r="K2">
+        <v>-1345</v>
+      </c>
+      <c r="L2">
+        <v>2440</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <v>1440</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>1200</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>2510</v>
+      </c>
+      <c r="I3">
+        <v>2510</v>
+      </c>
+      <c r="J3">
+        <v>2840</v>
+      </c>
+      <c r="K3">
+        <v>2040</v>
+      </c>
+      <c r="L3">
+        <v>-1300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>1200</v>
+      </c>
+      <c r="C4">
+        <v>1200</v>
+      </c>
+      <c r="D4">
+        <v>1200</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>1440</v>
+      </c>
+      <c r="G4">
+        <v>1200</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>-2100</v>
+      </c>
+      <c r="K4">
+        <v>2040</v>
+      </c>
+      <c r="L4">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>-1440</v>
+      </c>
+      <c r="C5">
+        <v>-1440</v>
+      </c>
+      <c r="D5" s="4">
+        <v>0</v>
+      </c>
+      <c r="E5" s="4">
+        <v>0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <v>-1440</v>
+      </c>
+      <c r="H5">
+        <v>1650</v>
+      </c>
+      <c r="I5">
+        <v>1650</v>
+      </c>
+      <c r="J5">
+        <v>2840</v>
+      </c>
+      <c r="K5">
+        <v>2040</v>
+      </c>
+      <c r="L5">
+        <v>-1440</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>-1440</v>
+      </c>
+      <c r="C6">
+        <v>-1440</v>
+      </c>
+      <c r="D6" s="4">
+        <v>0</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>-1440</v>
+      </c>
+      <c r="H6">
+        <v>2560</v>
+      </c>
+      <c r="I6">
+        <v>2560</v>
+      </c>
+      <c r="J6">
+        <v>2840</v>
+      </c>
+      <c r="K6">
+        <v>2040</v>
+      </c>
+      <c r="L6">
+        <v>-1440</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2">
-        <v>0</v>
-      </c>
-      <c r="C2">
-        <v>-25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2">
-        <v>3</v>
-      </c>
-      <c r="B3">
-        <v>-40</v>
-      </c>
-      <c r="C3">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="17.25" customHeight="1" x14ac:dyDescent="0.25"/>
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>1440</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>1440</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>-1200</v>
+      </c>
+      <c r="I7">
+        <v>-1200</v>
+      </c>
+      <c r="J7">
+        <v>2840</v>
+      </c>
+      <c r="K7">
+        <v>2040</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>1070</v>
+      </c>
+      <c r="D8">
+        <v>1070</v>
+      </c>
+      <c r="E8">
+        <v>1070</v>
+      </c>
+      <c r="F8">
+        <v>1070</v>
+      </c>
+      <c r="G8">
+        <v>1110</v>
+      </c>
+      <c r="H8">
+        <v>1070</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>-2100</v>
+      </c>
+      <c r="K8">
+        <v>-1345</v>
+      </c>
+      <c r="L8">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" s="3">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3">
+        <v>0</v>
+      </c>
+      <c r="D9">
+        <v>-2210</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>1200</v>
+      </c>
+      <c r="G9">
+        <v>-1350</v>
+      </c>
+      <c r="H9">
+        <v>-1200</v>
+      </c>
+      <c r="I9">
+        <v>2440</v>
+      </c>
+      <c r="J9">
+        <v>-2100</v>
+      </c>
+      <c r="K9" s="3">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>-1350</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
